--- a/update-vue-ensemble/ig/StructureDefinition-MatriculeINS.xlsx
+++ b/update-vue-ensemble/ig/StructureDefinition-MatriculeINS.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T15:02:21+00:00</t>
+    <t>2026-06-19T15:56:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
